--- a/artfynd/A 42189-2024 artfynd.xlsx
+++ b/artfynd/A 42189-2024 artfynd.xlsx
@@ -5160,7 +5160,7 @@
         <v>136339094</v>
       </c>
       <c r="B44" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 42189-2024 artfynd.xlsx
+++ b/artfynd/A 42189-2024 artfynd.xlsx
@@ -5160,7 +5160,7 @@
         <v>136339094</v>
       </c>
       <c r="B44" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 42189-2024 artfynd.xlsx
+++ b/artfynd/A 42189-2024 artfynd.xlsx
@@ -5160,7 +5160,7 @@
         <v>136339094</v>
       </c>
       <c r="B44" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 42189-2024 artfynd.xlsx
+++ b/artfynd/A 42189-2024 artfynd.xlsx
@@ -5160,7 +5160,7 @@
         <v>136339094</v>
       </c>
       <c r="B44" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 42189-2024 artfynd.xlsx
+++ b/artfynd/A 42189-2024 artfynd.xlsx
@@ -5160,7 +5160,7 @@
         <v>136339094</v>
       </c>
       <c r="B44" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 42189-2024 artfynd.xlsx
+++ b/artfynd/A 42189-2024 artfynd.xlsx
@@ -5160,7 +5160,7 @@
         <v>136339094</v>
       </c>
       <c r="B44" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
